--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -590,8 +590,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -616,6 +617,12 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <u val="single"/>
       <sz val="14"/>
       <name val="Liberation Serif;Times New Roman"/>
@@ -635,12 +642,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val=""/>
       <family val="1"/>
@@ -654,12 +655,18 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -696,7 +703,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -706,11 +713,11 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -718,6 +725,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -848,11 +867,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="49.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="96.97"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.89"/>
@@ -862,45 +881,45 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-    </row>
-    <row r="3" s="5" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" s="2" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -912,17 +931,17 @@
       <c r="E4" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="8" t="n">
         <f aca="false">G4*E4</f>
         <v>6.75</v>
       </c>
-      <c r="G4" s="1" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G4" s="8" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -934,27 +953,27 @@
       <c r="E5" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="F5" s="8" t="n">
         <f aca="false">E5*G5</f>
         <v>6.75</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="8" t="n">
         <f aca="false">G4</f>
         <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="9"/>
+      <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="D6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="n">
@@ -967,15 +986,15 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="5"/>
       <c r="C7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="6" t="n">
+      <c r="D7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="n">
@@ -987,9 +1006,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
@@ -1001,18 +1020,18 @@
       <c r="E8" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="F8" s="8" t="n">
         <f aca="false">E8*G8</f>
         <v>45</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="8" t="n">
         <f aca="false">G7</f>
         <v>45</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="6" t="s">
         <v>19</v>
       </c>
@@ -1022,27 +1041,27 @@
       <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="8" t="n">
         <f aca="false">E9*G9</f>
         <v>45</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="8" t="n">
         <f aca="false">G8</f>
         <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="9"/>
+      <c r="B10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="D10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F10" s="1" t="n">
@@ -1055,15 +1074,15 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6" t="s">
+      <c r="A11" s="9"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="6" t="n">
+      <c r="D11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F11" s="1" t="n">
@@ -1076,17 +1095,17 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="9"/>
+      <c r="B12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6" t="n">
+      <c r="D12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="1" t="n">
@@ -1099,15 +1118,15 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6" t="s">
+      <c r="A13" s="9"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="6" t="n">
+      <c r="D13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="1" t="n">
@@ -1120,17 +1139,17 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="9"/>
+      <c r="B14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="6" t="n">
+      <c r="D14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="n">
@@ -1143,15 +1162,15 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="6" t="n">
+      <c r="D15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="n">
@@ -1164,17 +1183,17 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="9"/>
+      <c r="B16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="6" t="n">
+      <c r="D16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="n">
@@ -1187,15 +1206,15 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6" t="s">
+      <c r="A17" s="9"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="6" t="n">
+      <c r="D17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="n">
@@ -1208,17 +1227,17 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="9"/>
+      <c r="B18" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="6" t="n">
+      <c r="D18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="n">
@@ -1231,15 +1250,15 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6" t="s">
+      <c r="A19" s="9"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="6" t="n">
+      <c r="D19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="1" t="n">
@@ -1250,12 +1269,20 @@
         <f aca="false">G18</f>
         <v>45</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="2" t="n">
+        <f aca="false">SUM(F10:F19)</f>
+        <v>495</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <f aca="false">H19/60</f>
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="20" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>36</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -1267,25 +1294,25 @@
       <c r="E20" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="8" t="n">
         <f aca="false">E20*G20</f>
         <v>22.5</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="8" t="n">
         <f aca="false">G19</f>
         <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6" t="s">
+      <c r="A21" s="9"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="6" t="n">
+      <c r="D21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F21" s="1" t="n">
@@ -1298,17 +1325,17 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="9"/>
+      <c r="B22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="6" t="n">
+      <c r="D22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F22" s="1" t="n">
@@ -1321,15 +1348,15 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6" t="s">
+      <c r="A23" s="9"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="6" t="n">
+      <c r="D23" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F23" s="1" t="n">
@@ -1342,17 +1369,17 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="9"/>
+      <c r="B24" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="6" t="n">
+      <c r="D24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F24" s="1" t="n">
@@ -1365,15 +1392,15 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6" t="s">
+      <c r="A25" s="9"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="6" t="n">
+      <c r="D25" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F25" s="1" t="n">
@@ -1385,18 +1412,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="6" t="s">
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9"/>
+      <c r="B26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="6" t="n">
+      <c r="D26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F26" s="1" t="n">
@@ -1409,15 +1436,15 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6" t="s">
+      <c r="A27" s="9"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="6" t="n">
+      <c r="D27" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F27" s="1" t="n">
@@ -1429,20 +1456,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="6" t="n">
+      <c r="D28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F28" s="1" t="n">
@@ -1455,15 +1482,15 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6" t="s">
+      <c r="A29" s="9"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="6" t="n">
+      <c r="D29" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F29" s="1" t="n">
@@ -1476,17 +1503,17 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6" t="s">
+      <c r="A30" s="9"/>
+      <c r="B30" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="6" t="n">
+      <c r="D30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F30" s="1" t="n">
@@ -1499,15 +1526,15 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6" t="s">
+      <c r="A31" s="9"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="6" t="n">
+      <c r="D31" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F31" s="1" t="n">
@@ -1520,17 +1547,17 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6" t="s">
+      <c r="A32" s="9"/>
+      <c r="B32" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="6" t="n">
+      <c r="D32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F32" s="1" t="n">
@@ -1543,15 +1570,15 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6" t="s">
+      <c r="A33" s="9"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="6" t="n">
+      <c r="D33" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F33" s="1" t="n">
@@ -1564,17 +1591,17 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6" t="s">
+      <c r="A34" s="9"/>
+      <c r="B34" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="6" t="n">
+      <c r="D34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F34" s="1" t="n">
@@ -1587,15 +1614,15 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="6" t="n">
+      <c r="D35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F35" s="1" t="n">
@@ -1608,17 +1635,17 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6" t="s">
+      <c r="A36" s="9"/>
+      <c r="B36" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="6" t="n">
+      <c r="D36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="n">
@@ -1631,15 +1658,15 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="6" t="n">
+      <c r="D37" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="n">
@@ -1652,17 +1679,17 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6" t="s">
+      <c r="A38" s="9"/>
+      <c r="B38" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="6" t="n">
+      <c r="D38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="n">
@@ -1675,15 +1702,15 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6" t="s">
+      <c r="A39" s="9"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="6" t="n">
+      <c r="D39" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="n">
@@ -1696,17 +1723,17 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6" t="s">
+      <c r="A40" s="9"/>
+      <c r="B40" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="6" t="n">
+      <c r="D40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="n">
@@ -1719,15 +1746,15 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6" t="s">
+      <c r="A41" s="9"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="6" t="n">
+      <c r="D41" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="1" t="n">
@@ -1740,17 +1767,17 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6" t="s">
+      <c r="A42" s="9"/>
+      <c r="B42" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="6" t="n">
+      <c r="D42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F42" s="1" t="n">
@@ -1763,15 +1790,15 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6" t="s">
+      <c r="A43" s="9"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="6" t="n">
+      <c r="D43" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.5</v>
       </c>
       <c r="F43" s="1" t="n">
@@ -1784,17 +1811,17 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6" t="s">
+      <c r="A44" s="9"/>
+      <c r="B44" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="6" t="n">
+      <c r="D44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="n">
@@ -1807,15 +1834,15 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6" t="s">
+      <c r="A45" s="9"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="6" t="n">
+      <c r="D45" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="n">
@@ -1828,17 +1855,17 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6" t="s">
+      <c r="A46" s="9"/>
+      <c r="B46" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="6" t="n">
+      <c r="D46" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="1" t="n">
@@ -1851,15 +1878,15 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6" t="s">
+      <c r="A47" s="9"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="6" t="n">
+      <c r="D47" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="n">
@@ -1872,17 +1899,17 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6" t="s">
+      <c r="A48" s="9"/>
+      <c r="B48" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="6" t="n">
+      <c r="D48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="1" t="n">
@@ -1895,15 +1922,15 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6" t="s">
+      <c r="A49" s="9"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="6" t="n">
+      <c r="D49" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="n">
@@ -1915,20 +1942,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="6" t="n">
+      <c r="D50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="1" t="n">
@@ -1941,15 +1968,15 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6" t="s">
+      <c r="A51" s="9"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="6" t="n">
+      <c r="D51" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="1" t="n">
@@ -1961,18 +1988,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6" t="s">
+    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9"/>
+      <c r="B52" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="6" t="n">
+      <c r="D52" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="n">
@@ -1985,15 +2012,15 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6" t="s">
+      <c r="A53" s="9"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="6" t="n">
+      <c r="D53" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="n">
@@ -2006,17 +2033,17 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6" t="s">
+      <c r="A54" s="9"/>
+      <c r="B54" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="6" t="n">
+      <c r="C54" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="1" t="n">
@@ -2029,15 +2056,15 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6" t="s">
+      <c r="A55" s="9"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="6" t="n">
+      <c r="D55" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="1" t="n">
@@ -2050,17 +2077,17 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6" t="s">
+      <c r="A56" s="9"/>
+      <c r="B56" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="6" t="n">
+      <c r="D56" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="n">
@@ -2073,15 +2100,15 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6" t="s">
+      <c r="A57" s="9"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="6" t="n">
+      <c r="D57" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="n">
@@ -2094,17 +2121,17 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6" t="s">
+      <c r="A58" s="9"/>
+      <c r="B58" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="6" t="n">
+      <c r="D58" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="n">
@@ -2117,15 +2144,15 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6" t="s">
+      <c r="A59" s="9"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="6" t="n">
+      <c r="D59" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="n">
@@ -2138,17 +2165,17 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6" t="s">
+      <c r="A60" s="9"/>
+      <c r="B60" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="6" t="n">
+      <c r="D60" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="n">
@@ -2161,15 +2188,15 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6" t="s">
+      <c r="A61" s="9"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="6" t="n">
+      <c r="D61" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="n">
@@ -2182,17 +2209,17 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6" t="s">
+      <c r="A62" s="9"/>
+      <c r="B62" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="6" t="n">
+      <c r="D62" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="n">
@@ -2205,15 +2232,15 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6" t="s">
+      <c r="A63" s="9"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="6" t="n">
+      <c r="D63" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="n">
@@ -2226,17 +2253,17 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6" t="s">
+      <c r="A64" s="9"/>
+      <c r="B64" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="6" t="n">
+      <c r="D64" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="n">
@@ -2249,15 +2276,15 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6" t="s">
+      <c r="A65" s="9"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="6" t="n">
+      <c r="D65" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="n">
@@ -2269,20 +2296,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="s">
+    <row r="66" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="6" t="n">
+      <c r="D66" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="n">
@@ -2295,15 +2322,15 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6" t="s">
+      <c r="A67" s="9"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="6" t="n">
+      <c r="D67" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="n">
@@ -2316,17 +2343,17 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6" t="s">
+      <c r="A68" s="9"/>
+      <c r="B68" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="6" t="n">
+      <c r="D68" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="1" t="n">
@@ -2339,15 +2366,15 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6" t="s">
+      <c r="A69" s="9"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="6" t="n">
+      <c r="D69" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="n">
@@ -2360,17 +2387,17 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6" t="s">
+      <c r="A70" s="9"/>
+      <c r="B70" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="6" t="n">
+      <c r="D70" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="n">
@@ -2383,15 +2410,15 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6" t="s">
+      <c r="A71" s="9"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="D71" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="6" t="n">
+      <c r="D71" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="F71" s="1" t="n">
@@ -2404,17 +2431,17 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6" t="s">
+      <c r="A72" s="9"/>
+      <c r="B72" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="6" t="n">
+      <c r="D72" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="1" t="n">
@@ -2427,15 +2454,15 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6" t="s">
+      <c r="A73" s="9"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="D73" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="6" t="n">
+      <c r="D73" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="n">
@@ -2448,17 +2475,17 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6" t="s">
+      <c r="A74" s="9"/>
+      <c r="B74" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="6" t="n">
+      <c r="D74" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="n">
@@ -2471,15 +2498,15 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6" t="s">
+      <c r="A75" s="9"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="6" t="n">
+      <c r="D75" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="n">
@@ -2492,17 +2519,17 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6" t="s">
+      <c r="A76" s="9"/>
+      <c r="B76" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D76" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="6" t="n">
+      <c r="D76" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F76" s="1" t="n">
@@ -2515,15 +2542,15 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6" t="s">
+      <c r="A77" s="9"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="6" t="n">
+      <c r="D77" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F77" s="1" t="n">
@@ -2536,17 +2563,17 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6" t="s">
+      <c r="A78" s="9"/>
+      <c r="B78" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="D78" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="6" t="n">
+      <c r="D78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F78" s="1" t="n">
@@ -2559,15 +2586,15 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6" t="s">
+      <c r="A79" s="9"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="6" t="n">
+      <c r="D79" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F79" s="1" t="n">
@@ -2580,17 +2607,17 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6" t="s">
+      <c r="A80" s="9"/>
+      <c r="B80" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D80" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="6" t="n">
+      <c r="D80" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F80" s="1" t="n">
@@ -2603,15 +2630,15 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6" t="s">
+      <c r="A81" s="9"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D81" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="6" t="n">
+      <c r="D81" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F81" s="1" t="n">
@@ -2624,17 +2651,17 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6" t="s">
+      <c r="A82" s="9"/>
+      <c r="B82" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="D82" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="6" t="n">
+      <c r="D82" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F82" s="1" t="n">
@@ -2647,15 +2674,15 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6" t="s">
+      <c r="A83" s="9"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="6" t="n">
+      <c r="D83" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F83" s="1" t="n">
@@ -2667,20 +2694,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="s">
+    <row r="84" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="B84" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="6" t="n">
+      <c r="D84" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F84" s="1" t="n">
@@ -2693,15 +2720,15 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6" t="s">
+      <c r="A85" s="9"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="6" t="n">
+      <c r="D85" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="1" t="n">
@@ -2714,17 +2741,17 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6" t="s">
+      <c r="A86" s="9"/>
+      <c r="B86" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D86" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="6" t="n">
+      <c r="D86" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="1" t="n">
@@ -2737,15 +2764,15 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6" t="s">
+      <c r="A87" s="9"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="D87" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="6" t="n">
+      <c r="D87" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F87" s="1" t="n">
@@ -2758,17 +2785,17 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6" t="s">
+      <c r="A88" s="9"/>
+      <c r="B88" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D88" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="6" t="n">
+      <c r="D88" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F88" s="1" t="n">
@@ -2781,15 +2808,15 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6" t="s">
+      <c r="A89" s="9"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="D89" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="6" t="n">
+      <c r="D89" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F89" s="1" t="n">
@@ -2802,17 +2829,17 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6" t="s">
+      <c r="A90" s="9"/>
+      <c r="B90" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="D90" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="6" t="n">
+      <c r="D90" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F90" s="1" t="n">
@@ -2825,15 +2852,15 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6" t="s">
+      <c r="A91" s="9"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D91" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="6" t="n">
+      <c r="D91" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F91" s="1" t="n">
@@ -2845,20 +2872,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6" t="s">
+    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="B92" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C92" s="6" t="s">
+      <c r="C92" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="6" t="n">
+      <c r="D92" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F92" s="1" t="n">
@@ -2871,15 +2898,15 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6" t="s">
+      <c r="A93" s="9"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D93" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="6" t="n">
+      <c r="D93" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F93" s="1" t="n">
@@ -2892,17 +2919,17 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6" t="s">
+      <c r="A94" s="9"/>
+      <c r="B94" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C94" s="6" t="s">
+      <c r="C94" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D94" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="6" t="n">
+      <c r="D94" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="1" t="n">
@@ -2915,15 +2942,15 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6" t="s">
+      <c r="A95" s="9"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D95" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="6" t="n">
+      <c r="D95" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F95" s="1" t="n">
@@ -2936,17 +2963,17 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6" t="s">
+      <c r="A96" s="9"/>
+      <c r="B96" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="C96" s="6" t="s">
+      <c r="C96" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D96" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="6" t="n">
+      <c r="D96" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F96" s="1" t="n">
@@ -2959,15 +2986,15 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6" t="s">
+      <c r="A97" s="9"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="D97" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="6" t="n">
+      <c r="D97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F97" s="1" t="n">
@@ -2980,17 +3007,17 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6" t="s">
+      <c r="A98" s="9"/>
+      <c r="B98" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="C98" s="6" t="s">
+      <c r="C98" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="D98" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="6" t="n">
+      <c r="D98" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F98" s="1" t="n">
@@ -3003,15 +3030,15 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6" t="s">
+      <c r="A99" s="9"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="D99" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="6" t="n">
+      <c r="D99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F99" s="1" t="n">
@@ -3024,17 +3051,17 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6" t="s">
+      <c r="A100" s="9"/>
+      <c r="B100" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C100" s="6" t="s">
+      <c r="C100" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D100" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="6" t="n">
+      <c r="D100" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F100" s="1" t="n">
@@ -3047,15 +3074,15 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6" t="s">
+      <c r="A101" s="9"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D101" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="6" t="n">
+      <c r="D101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="1" t="n">
@@ -3067,20 +3094,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="55.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6" t="s">
+    <row r="102" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B102" s="6" t="s">
+      <c r="B102" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="C102" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="D102" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="6" t="n">
+      <c r="D102" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F102" s="1" t="n">
@@ -3093,15 +3120,15 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6" t="s">
+      <c r="A103" s="9"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D103" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="6" t="n">
+      <c r="D103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F103" s="1" t="n">
@@ -3114,17 +3141,17 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6" t="s">
+      <c r="A104" s="9"/>
+      <c r="B104" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C104" s="6" t="s">
+      <c r="C104" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="D104" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="6" t="n">
+      <c r="D104" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F104" s="1" t="n">
@@ -3137,15 +3164,15 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6" t="s">
+      <c r="A105" s="9"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="D105" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="6" t="n">
+      <c r="D105" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F105" s="1" t="n">
@@ -3158,17 +3185,17 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6" t="s">
+      <c r="A106" s="9"/>
+      <c r="B106" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C106" s="6" t="s">
+      <c r="C106" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="D106" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="6" t="n">
+      <c r="D106" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F106" s="1" t="n">
@@ -3181,15 +3208,15 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6" t="s">
+      <c r="A107" s="9"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="D107" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="6" t="n">
+      <c r="D107" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F107" s="1" t="n">
@@ -3201,18 +3228,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6" t="s">
+    <row r="108" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="9"/>
+      <c r="B108" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C108" s="6" t="s">
+      <c r="C108" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="D108" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="6" t="n">
+      <c r="D108" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F108" s="1" t="n">
@@ -3225,15 +3252,15 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6" t="s">
+      <c r="A109" s="9"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D109" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="6" t="n">
+      <c r="D109" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="1" t="n">
@@ -3246,13 +3273,13 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
-      <c r="E110" s="4" t="n">
+      <c r="B110" s="5"/>
+      <c r="C110" s="9"/>
+      <c r="D110" s="9"/>
+      <c r="E110" s="5" t="n">
         <v>149.8</v>
       </c>
       <c r="F110" s="1" t="n">
@@ -3261,17 +3288,17 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="3"/>
-      <c r="F111" s="5" t="n">
+      <c r="A111" s="4"/>
+      <c r="F111" s="2" t="n">
         <f aca="false">F110/60</f>
         <v>112.35</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="6"/>
-    </row>
-    <row r="113" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="4" t="s">
+      <c r="A112" s="9"/>
+    </row>
+    <row r="113" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="5" t="s">
         <v>178</v>
       </c>
     </row>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -1050,46 +1050,46 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9"/>
-      <c r="B10" s="5" t="s">
+    <row r="10" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6"/>
+      <c r="B10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="9" t="n">
+      <c r="D10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="F10" s="8" t="n">
         <f aca="false">E10*G10</f>
         <v>22.5</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="8" t="n">
         <f aca="false">G9</f>
         <v>45</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="9" t="s">
+    <row r="11" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="8" t="n">
         <f aca="false">E11*G11</f>
         <v>22.5</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="8" t="n">
         <f aca="false">G10</f>
         <v>45</v>
       </c>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -1094,25 +1094,25 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9"/>
-      <c r="B12" s="5" t="s">
+    <row r="12" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1" t="n">
+      <c r="D12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <f aca="false">E12*G12</f>
         <v>90</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="8" t="n">
         <f aca="false">G11</f>
         <v>45</v>
       </c>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -655,7 +655,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -666,6 +666,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF55308D"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
   </fills>
@@ -703,7 +709,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -744,6 +750,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -753,6 +771,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF55308D"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1117,23 +1195,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="9" t="s">
+    <row r="13" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="1" t="n">
+      <c r="D13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <f aca="false">E13*G13</f>
         <v>90</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="8" t="n">
         <f aca="false">G12</f>
         <v>45</v>
       </c>
@@ -1278,27 +1356,27 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="20" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+    <row r="20" s="12" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="6" t="n">
+      <c r="D20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="12" t="n">
         <f aca="false">E20*G20</f>
         <v>22.5</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G20" s="12" t="n">
         <f aca="false">G19</f>
         <v>45</v>
       </c>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -1216,25 +1216,25 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9"/>
-      <c r="B14" s="5" t="s">
+    <row r="14" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="D14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="8" t="n">
         <f aca="false">E14*G14</f>
         <v>45</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="8" t="n">
         <f aca="false">G13</f>
         <v>45</v>
       </c>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -1239,23 +1239,23 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="9" t="s">
+    <row r="15" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="8" t="n">
         <f aca="false">E15*G15</f>
         <v>45</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="8" t="n">
         <f aca="false">G14</f>
         <v>45</v>
       </c>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -1260,46 +1260,46 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9"/>
-      <c r="B16" s="5" t="s">
+    <row r="16" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="9" t="n">
+      <c r="D16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="8" t="n">
         <f aca="false">E16*G16</f>
         <v>45</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="8" t="n">
         <f aca="false">G15</f>
         <v>45</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="9" t="s">
+    <row r="17" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="9" t="n">
+      <c r="D17" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="8" t="n">
         <f aca="false">E17*G17</f>
         <v>45</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="8" t="n">
         <f aca="false">G16</f>
         <v>45</v>
       </c>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -136,34 +136,7 @@
     <t xml:space="preserve">Принципы VCS, преимущества Git</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val=""/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Установка Git, базовая настройка (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF0000FF"/>
-        <rFont val=""/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">user.name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val=""/>
-        <family val="1"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, user.email)</t>
-    </r>
+    <t xml:space="preserve">Установка Git, базовая настройка (user.name, user.email)</t>
   </si>
   <si>
     <t xml:space="preserve">2.2. Основные операции: фиксация и откат изменений, поиск, история</t>
@@ -594,11 +567,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -620,6 +594,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -627,31 +602,20 @@
       <sz val="14"/>
       <name val="Liberation Serif;Times New Roman"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Liberation Serif;Times New Roman"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <name val=""/>
-      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val=""/>
-      <family val="1"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF0000FF"/>
-      <name val=""/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -714,51 +678,51 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -950,7 +914,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="31.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="49.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="96.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="96.98"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.36"/>
@@ -970,20 +934,20 @@
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" s="2" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+    <row r="3" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -993,65 +957,65 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" s="7" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="7" t="n">
         <f aca="false">G4*E4</f>
         <v>6.75</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7" t="s">
+      <c r="G4" s="7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" s="7" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="D5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>0.15</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="F5" s="7" t="n">
         <f aca="false">E5*G5</f>
         <v>6.75</v>
       </c>
-      <c r="G5" s="8" t="n">
+      <c r="G5" s="7" t="n">
         <f aca="false">G4</f>
         <v>45</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9"/>
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8"/>
+      <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="9" t="n">
+      <c r="D6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="n">
@@ -1063,16 +1027,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="6" t="s">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8"/>
+      <c r="C7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="9" t="n">
+      <c r="D7" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="n">
@@ -1084,238 +1047,238 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="7" t="s">
+    <row r="8" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="D8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="7" t="n">
         <f aca="false">E8*G8</f>
         <v>45</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
         <f aca="false">G7</f>
         <v>45</v>
       </c>
     </row>
-    <row r="9" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="6" t="s">
+    <row r="9" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="6" t="n">
+      <c r="D9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="F9" s="7" t="n">
         <f aca="false">E9*G9</f>
         <v>45</v>
       </c>
-      <c r="G9" s="8" t="n">
+      <c r="G9" s="7" t="n">
         <f aca="false">G8</f>
         <v>45</v>
       </c>
     </row>
-    <row r="10" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7" t="s">
+    <row r="10" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="6" t="n">
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="7" t="n">
         <f aca="false">E10*G10</f>
         <v>22.5</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="G10" s="7" t="n">
         <f aca="false">G9</f>
         <v>45</v>
       </c>
     </row>
-    <row r="11" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="6" t="s">
+    <row r="11" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="6" t="n">
+      <c r="D11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="7" t="n">
         <f aca="false">E11*G11</f>
         <v>22.5</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="7" t="n">
         <f aca="false">G10</f>
         <v>45</v>
       </c>
     </row>
-    <row r="12" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6"/>
-      <c r="B12" s="7" t="s">
+    <row r="12" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="8" t="n">
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="7" t="n">
         <f aca="false">E12*G12</f>
         <v>90</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="7" t="n">
         <f aca="false">G11</f>
         <v>45</v>
       </c>
     </row>
-    <row r="13" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="6" t="s">
+    <row r="13" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="8" t="n">
+      <c r="D13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <f aca="false">E13*G13</f>
         <v>90</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="7" t="n">
         <f aca="false">G12</f>
         <v>45</v>
       </c>
     </row>
-    <row r="14" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7" t="s">
+    <row r="14" s="7" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="6" t="n">
+      <c r="D14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="7" t="n">
         <f aca="false">E14*G14</f>
         <v>45</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="7" t="n">
         <f aca="false">G13</f>
         <v>45</v>
       </c>
     </row>
-    <row r="15" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="6" t="s">
+    <row r="15" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="6" t="n">
+      <c r="D15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="8" t="n">
+      <c r="F15" s="7" t="n">
         <f aca="false">E15*G15</f>
         <v>45</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G15" s="7" t="n">
         <f aca="false">G14</f>
         <v>45</v>
       </c>
     </row>
-    <row r="16" s="8" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7" t="s">
+    <row r="16" s="7" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="6" t="n">
+      <c r="D16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="7" t="n">
         <f aca="false">E16*G16</f>
         <v>45</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G16" s="7" t="n">
         <f aca="false">G15</f>
         <v>45</v>
       </c>
     </row>
-    <row r="17" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="6" t="s">
+    <row r="17" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="6" t="n">
+      <c r="D17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="8" t="n">
+      <c r="F17" s="7" t="n">
         <f aca="false">E17*G17</f>
         <v>45</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G17" s="7" t="n">
         <f aca="false">G16</f>
         <v>45</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9"/>
-      <c r="B18" s="5" t="s">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8"/>
+      <c r="B18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="9" t="n">
+      <c r="D18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="1" t="n">
@@ -1327,16 +1290,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="9" t="s">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8"/>
+      <c r="C19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="9" t="n">
+      <c r="D19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="1" t="n">
@@ -1356,41 +1318,40 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="20" s="12" customFormat="true" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+    <row r="20" s="11" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="10" t="n">
+      <c r="D20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="11" t="n">
         <f aca="false">E20*G20</f>
         <v>22.5</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="11" t="n">
         <f aca="false">G19</f>
         <v>45</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="17.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="9" t="s">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8"/>
+      <c r="C21" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="9" t="n">
+      <c r="D21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F21" s="1" t="n">
@@ -1402,18 +1363,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9"/>
-      <c r="B22" s="5" t="s">
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8"/>
+      <c r="B22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="9" t="n">
+      <c r="D22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F22" s="1" t="n">
@@ -1425,16 +1386,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="9" t="s">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8"/>
+      <c r="C23" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="9" t="n">
+      <c r="D23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F23" s="1" t="n">
@@ -1446,18 +1406,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9"/>
-      <c r="B24" s="5" t="s">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8"/>
+      <c r="B24" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="9" t="n">
+      <c r="D24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F24" s="1" t="n">
@@ -1469,16 +1429,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="9" t="s">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8"/>
+      <c r="C25" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="9" t="n">
+      <c r="D25" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F25" s="1" t="n">
@@ -1490,18 +1449,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9"/>
-      <c r="B26" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="9" t="s">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8"/>
+      <c r="B26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="9" t="n">
+      <c r="D26" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F26" s="1" t="n">
@@ -1513,16 +1472,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="9" t="s">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8"/>
+      <c r="C27" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="9" t="n">
+      <c r="D27" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F27" s="1" t="n">
@@ -1534,20 +1492,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D28" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="9" t="n">
+      <c r="D28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F28" s="1" t="n">
@@ -1559,16 +1517,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="9" t="s">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8"/>
+      <c r="C29" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="9" t="n">
+      <c r="D29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F29" s="1" t="n">
@@ -1580,18 +1537,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9"/>
-      <c r="B30" s="5" t="s">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8"/>
+      <c r="B30" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="9" t="n">
+      <c r="D30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F30" s="1" t="n">
@@ -1603,16 +1560,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="9" t="s">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8"/>
+      <c r="C31" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="9" t="n">
+      <c r="D31" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F31" s="1" t="n">
@@ -1624,18 +1580,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="9"/>
-      <c r="B32" s="5" t="s">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8"/>
+      <c r="B32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="9" t="n">
+      <c r="D32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F32" s="1" t="n">
@@ -1647,16 +1603,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="9" t="s">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8"/>
+      <c r="C33" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E33" s="9" t="n">
+      <c r="D33" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E33" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F33" s="1" t="n">
@@ -1668,18 +1623,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9"/>
-      <c r="B34" s="5" t="s">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8"/>
+      <c r="B34" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="9" t="n">
+      <c r="D34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F34" s="1" t="n">
@@ -1691,16 +1646,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="9" t="s">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8"/>
+      <c r="C35" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F35" s="1" t="n">
@@ -1712,18 +1666,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9"/>
-      <c r="B36" s="5" t="s">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8"/>
+      <c r="B36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="9" t="n">
+      <c r="D36" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="1" t="n">
@@ -1735,16 +1689,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="9" t="s">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8"/>
+      <c r="C37" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="9" t="n">
+      <c r="D37" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="1" t="n">
@@ -1756,18 +1709,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9"/>
-      <c r="B38" s="5" t="s">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8"/>
+      <c r="B38" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D38" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="1" t="n">
@@ -1779,16 +1732,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="9"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="9" t="s">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8"/>
+      <c r="C39" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E39" s="9" t="n">
+      <c r="D39" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F39" s="1" t="n">
@@ -1800,18 +1752,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="9"/>
-      <c r="B40" s="5" t="s">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8"/>
+      <c r="B40" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="9" t="n">
+      <c r="D40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="1" t="n">
@@ -1823,16 +1775,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="9"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="9" t="s">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8"/>
+      <c r="C41" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="9" t="n">
+      <c r="D41" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="1" t="n">
@@ -1844,18 +1795,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9"/>
-      <c r="B42" s="5" t="s">
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8"/>
+      <c r="B42" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D42" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="9" t="n">
+      <c r="D42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F42" s="1" t="n">
@@ -1867,16 +1818,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="9" t="s">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8"/>
+      <c r="C43" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="9" t="n">
+      <c r="D43" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="8" t="n">
         <v>0.5</v>
       </c>
       <c r="F43" s="1" t="n">
@@ -1888,18 +1838,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9"/>
-      <c r="B44" s="5" t="s">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8"/>
+      <c r="B44" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="9" t="n">
+      <c r="D44" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F44" s="1" t="n">
@@ -1911,16 +1861,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="9" t="s">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8"/>
+      <c r="C45" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="9" t="n">
+      <c r="D45" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F45" s="1" t="n">
@@ -1932,18 +1881,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9"/>
-      <c r="B46" s="5" t="s">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8"/>
+      <c r="B46" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="1" t="n">
@@ -1955,16 +1904,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="9" t="s">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8"/>
+      <c r="C47" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E47" s="9" t="n">
+      <c r="D47" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F47" s="1" t="n">
@@ -1976,18 +1924,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="5" t="s">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8"/>
+      <c r="B48" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D48" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="9" t="n">
+      <c r="D48" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="1" t="n">
@@ -1999,16 +1947,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="9" t="s">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8"/>
+      <c r="C49" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E49" s="9" t="n">
+      <c r="D49" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F49" s="1" t="n">
@@ -2020,20 +1967,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="s">
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="D50" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="9" t="n">
+      <c r="D50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="1" t="n">
@@ -2045,16 +1992,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="9" t="s">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8"/>
+      <c r="C51" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="9" t="n">
+      <c r="D51" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="1" t="n">
@@ -2066,18 +2012,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
-      <c r="B52" s="5" t="s">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8"/>
+      <c r="B52" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D52" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="9" t="n">
+      <c r="D52" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F52" s="1" t="n">
@@ -2089,16 +2035,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="9" t="s">
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8"/>
+      <c r="C53" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E53" s="9" t="n">
+      <c r="D53" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F53" s="1" t="n">
@@ -2110,18 +2055,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="9"/>
-      <c r="B54" s="5" t="s">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8"/>
+      <c r="B54" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="9" t="n">
+      <c r="C54" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="1" t="n">
@@ -2133,16 +2078,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="9" t="s">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8"/>
+      <c r="C55" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D55" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E55" s="9" t="n">
+      <c r="D55" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="1" t="n">
@@ -2154,18 +2098,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9"/>
-      <c r="B56" s="5" t="s">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="8"/>
+      <c r="B56" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="C56" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D56" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="9" t="n">
+      <c r="D56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F56" s="1" t="n">
@@ -2177,16 +2121,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="9" t="s">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8"/>
+      <c r="C57" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D57" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E57" s="9" t="n">
+      <c r="D57" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F57" s="1" t="n">
@@ -2198,18 +2141,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="9"/>
-      <c r="B58" s="5" t="s">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8"/>
+      <c r="B58" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D58" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="9" t="n">
+      <c r="D58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F58" s="1" t="n">
@@ -2221,16 +2164,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="9"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="9" t="s">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8"/>
+      <c r="C59" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E59" s="9" t="n">
+      <c r="D59" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F59" s="1" t="n">
@@ -2242,18 +2184,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="9"/>
-      <c r="B60" s="5" t="s">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="8"/>
+      <c r="B60" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C60" s="9" t="s">
+      <c r="C60" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D60" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="9" t="n">
+      <c r="D60" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F60" s="1" t="n">
@@ -2265,16 +2207,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="9"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="9" t="s">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="8"/>
+      <c r="C61" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D61" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="9" t="n">
+      <c r="D61" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F61" s="1" t="n">
@@ -2286,18 +2227,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="9"/>
-      <c r="B62" s="5" t="s">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="8"/>
+      <c r="B62" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C62" s="9" t="s">
+      <c r="C62" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="D62" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="9" t="n">
+      <c r="D62" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F62" s="1" t="n">
@@ -2309,16 +2250,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="9"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="9" t="s">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8"/>
+      <c r="C63" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D63" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E63" s="9" t="n">
+      <c r="D63" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F63" s="1" t="n">
@@ -2330,18 +2270,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="9"/>
-      <c r="B64" s="5" t="s">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8"/>
+      <c r="B64" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C64" s="9" t="s">
+      <c r="C64" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D64" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="9" t="n">
+      <c r="D64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F64" s="1" t="n">
@@ -2353,16 +2293,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="9"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="9" t="s">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="8"/>
+      <c r="C65" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="9" t="n">
+      <c r="D65" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F65" s="1" t="n">
@@ -2374,20 +2313,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="9" t="s">
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C66" s="9" t="s">
+      <c r="C66" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="9" t="n">
+      <c r="D66" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F66" s="1" t="n">
@@ -2399,16 +2338,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="9"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="9" t="s">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="8"/>
+      <c r="C67" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="D67" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E67" s="9" t="n">
+      <c r="D67" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F67" s="1" t="n">
@@ -2420,18 +2358,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="9"/>
-      <c r="B68" s="5" t="s">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="8"/>
+      <c r="B68" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C68" s="9" t="s">
+      <c r="C68" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="D68" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="9" t="n">
+      <c r="D68" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="1" t="n">
@@ -2443,16 +2381,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="9"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="9" t="s">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8"/>
+      <c r="C69" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E69" s="9" t="n">
+      <c r="D69" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F69" s="1" t="n">
@@ -2464,18 +2401,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="9"/>
-      <c r="B70" s="5" t="s">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8"/>
+      <c r="B70" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C70" s="9" t="s">
+      <c r="C70" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D70" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="9" t="n">
+      <c r="D70" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F70" s="1" t="n">
@@ -2487,16 +2424,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="9"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="9" t="s">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8"/>
+      <c r="C71" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="D71" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="9" t="n">
+      <c r="D71" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" s="8" t="n">
         <v>1.5</v>
       </c>
       <c r="F71" s="1" t="n">
@@ -2508,18 +2444,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="9"/>
-      <c r="B72" s="5" t="s">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8"/>
+      <c r="B72" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="9" t="n">
+      <c r="D72" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="1" t="n">
@@ -2531,16 +2467,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="9"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="9" t="s">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8"/>
+      <c r="C73" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="9" t="n">
+      <c r="D73" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F73" s="1" t="n">
@@ -2552,18 +2487,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="9"/>
-      <c r="B74" s="5" t="s">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8"/>
+      <c r="B74" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="9" t="n">
+      <c r="D74" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F74" s="1" t="n">
@@ -2575,16 +2510,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="9"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="9" t="s">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8"/>
+      <c r="C75" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="9" t="n">
+      <c r="D75" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F75" s="1" t="n">
@@ -2596,18 +2530,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="9"/>
-      <c r="B76" s="5" t="s">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="8"/>
+      <c r="B76" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D76" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="9" t="n">
+      <c r="D76" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F76" s="1" t="n">
@@ -2619,16 +2553,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="9"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="9" t="s">
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="8"/>
+      <c r="C77" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="9" t="n">
+      <c r="D77" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F77" s="1" t="n">
@@ -2640,18 +2573,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="9"/>
-      <c r="B78" s="5" t="s">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="8"/>
+      <c r="B78" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="9" t="n">
+      <c r="D78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F78" s="1" t="n">
@@ -2663,16 +2596,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="9"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="9" t="s">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8"/>
+      <c r="C79" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="D79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="9" t="n">
+      <c r="D79" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F79" s="1" t="n">
@@ -2684,18 +2616,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="9"/>
-      <c r="B80" s="5" t="s">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8"/>
+      <c r="B80" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D80" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="9" t="n">
+      <c r="D80" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F80" s="1" t="n">
@@ -2707,16 +2639,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="9"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="9" t="s">
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8"/>
+      <c r="C81" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="9" t="n">
+      <c r="D81" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F81" s="1" t="n">
@@ -2728,18 +2659,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="9"/>
-      <c r="B82" s="5" t="s">
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8"/>
+      <c r="B82" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="C82" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D82" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="9" t="n">
+      <c r="D82" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F82" s="1" t="n">
@@ -2751,16 +2682,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="9"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="9" t="s">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="8"/>
+      <c r="C83" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="9" t="n">
+      <c r="D83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F83" s="1" t="n">
@@ -2772,20 +2702,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="9" t="s">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C84" s="9" t="s">
+      <c r="C84" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D84" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="9" t="n">
+      <c r="D84" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F84" s="1" t="n">
@@ -2797,16 +2727,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="9"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="9" t="s">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8"/>
+      <c r="C85" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="9" t="n">
+      <c r="D85" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="1" t="n">
@@ -2818,18 +2747,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="9"/>
-      <c r="B86" s="5" t="s">
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8"/>
+      <c r="B86" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C86" s="9" t="s">
+      <c r="C86" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D86" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="9" t="n">
+      <c r="D86" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="1" t="n">
@@ -2841,16 +2770,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="9"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="9" t="s">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8"/>
+      <c r="C87" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="9" t="n">
+      <c r="D87" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F87" s="1" t="n">
@@ -2862,18 +2790,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="9"/>
-      <c r="B88" s="5" t="s">
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8"/>
+      <c r="B88" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C88" s="9" t="s">
+      <c r="C88" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D88" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="9" t="n">
+      <c r="D88" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F88" s="1" t="n">
@@ -2885,16 +2813,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="9"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="9" t="s">
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8"/>
+      <c r="C89" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="9" t="n">
+      <c r="D89" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F89" s="1" t="n">
@@ -2906,18 +2833,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="9"/>
-      <c r="B90" s="5" t="s">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8"/>
+      <c r="B90" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C90" s="9" t="s">
+      <c r="C90" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D90" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="9" t="n">
+      <c r="D90" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F90" s="1" t="n">
@@ -2929,16 +2856,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="9"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="9" t="s">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8"/>
+      <c r="C91" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="9" t="n">
+      <c r="D91" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F91" s="1" t="n">
@@ -2950,20 +2876,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="9" t="s">
+    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D92" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="9" t="n">
+      <c r="D92" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F92" s="1" t="n">
@@ -2975,16 +2901,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="9"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="9" t="s">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="8"/>
+      <c r="C93" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="9" t="n">
+      <c r="D93" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F93" s="1" t="n">
@@ -2996,18 +2921,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="9"/>
-      <c r="B94" s="5" t="s">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8"/>
+      <c r="B94" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="C94" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D94" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="9" t="n">
+      <c r="D94" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F94" s="1" t="n">
@@ -3019,16 +2944,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="9"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="9" t="s">
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8"/>
+      <c r="C95" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="9" t="n">
+      <c r="D95" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F95" s="1" t="n">
@@ -3040,18 +2964,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="9"/>
-      <c r="B96" s="5" t="s">
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="8"/>
+      <c r="B96" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C96" s="9" t="s">
+      <c r="C96" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D96" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="9" t="n">
+      <c r="D96" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F96" s="1" t="n">
@@ -3063,16 +2987,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="9"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="9" t="s">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8"/>
+      <c r="C97" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="9" t="n">
+      <c r="D97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F97" s="1" t="n">
@@ -3084,18 +3007,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="9"/>
-      <c r="B98" s="5" t="s">
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="8"/>
+      <c r="B98" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C98" s="9" t="s">
+      <c r="C98" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D98" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="9" t="n">
+      <c r="D98" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F98" s="1" t="n">
@@ -3107,16 +3030,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="9"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="9" t="s">
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8"/>
+      <c r="C99" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="9" t="n">
+      <c r="D99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F99" s="1" t="n">
@@ -3128,18 +3050,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="9"/>
-      <c r="B100" s="5" t="s">
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="8"/>
+      <c r="B100" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C100" s="9" t="s">
+      <c r="C100" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="D100" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="9" t="n">
+      <c r="D100" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F100" s="1" t="n">
@@ -3151,16 +3073,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="9"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="9" t="s">
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8"/>
+      <c r="C101" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="9" t="n">
+      <c r="D101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F101" s="1" t="n">
@@ -3172,20 +3093,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="9" t="s">
+    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C102" s="9" t="s">
+      <c r="C102" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D102" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="9" t="n">
+      <c r="D102" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F102" s="1" t="n">
@@ -3197,16 +3118,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="9"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="9" t="s">
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="8"/>
+      <c r="C103" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="9" t="n">
+      <c r="D103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F103" s="1" t="n">
@@ -3218,18 +3138,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="9"/>
-      <c r="B104" s="5" t="s">
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="8"/>
+      <c r="B104" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C104" s="9" t="s">
+      <c r="C104" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D104" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="9" t="n">
+      <c r="D104" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F104" s="1" t="n">
@@ -3241,16 +3161,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="9"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="9" t="s">
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="8"/>
+      <c r="C105" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="D105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="9" t="n">
+      <c r="D105" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F105" s="1" t="n">
@@ -3262,18 +3181,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="9"/>
-      <c r="B106" s="5" t="s">
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="8"/>
+      <c r="B106" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C106" s="9" t="s">
+      <c r="C106" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D106" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="9" t="n">
+      <c r="D106" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F106" s="1" t="n">
@@ -3285,16 +3204,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="9"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="9" t="s">
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="8"/>
+      <c r="C107" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="9" t="n">
+      <c r="D107" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="8" t="n">
         <v>2</v>
       </c>
       <c r="F107" s="1" t="n">
@@ -3306,18 +3224,18 @@
         <v>45</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="9"/>
-      <c r="B108" s="5" t="s">
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="8"/>
+      <c r="B108" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D108" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="9" t="n">
+      <c r="D108" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F108" s="1" t="n">
@@ -3329,16 +3247,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="9"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="9" t="s">
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="8"/>
+      <c r="C109" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="D109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="9" t="n">
+      <c r="D109" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="1" t="n">
@@ -3350,14 +3267,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="9" t="s">
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B110" s="5"/>
-      <c r="C110" s="9"/>
-      <c r="D110" s="9"/>
-      <c r="E110" s="5" t="n">
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="2" t="n">
         <v>149.8</v>
       </c>
       <c r="F110" s="1" t="n">
@@ -3373,10 +3289,10 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="9"/>
-    </row>
-    <row r="113" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="5" t="s">
+      <c r="A112" s="8"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3385,7 +3301,7 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C21" r:id="rId1" display="user.name"/>
+    <hyperlink ref="C21" r:id="rId1" display="Установка Git, базовая настройка (user.name, user.email)"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/cpp_course_program.xlsx
+++ b/cpp_course_program.xlsx
@@ -673,7 +673,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -707,6 +707,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1267,85 +1271,86 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
-      <c r="B18" s="2" t="s">
+    <row r="18" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="8" t="n">
+      <c r="D18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="7" t="n">
         <f aca="false">E18*G18</f>
         <v>45</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="7" t="n">
         <f aca="false">G17</f>
         <v>45</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8"/>
-      <c r="C19" s="8" t="s">
+    <row r="19" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="8" t="n">
+      <c r="D19" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="7" t="n">
         <f aca="false">E19*G19</f>
         <v>45</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="7" t="n">
         <f aca="false">G18</f>
         <v>45</v>
       </c>
-      <c r="H19" s="2" t="n">
+      <c r="H19" s="9" t="n">
         <f aca="false">SUM(F10:F19)</f>
         <v>495</v>
       </c>
-      <c r="I19" s="2" t="n">
+      <c r="I19" s="9" t="n">
         <f aca="false">H19/60</f>
         <v>8.25</v>
       </c>
     </row>
-    <row r="20" s="11" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
+    <row r="20" s="12" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="9" t="n">
+      <c r="D20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <f aca="false">E20*G20</f>
         <v>22.5</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="12" t="n">
         <f aca="false">G19</f>
         <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8"/>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D21" s="8" t="s">
